--- a/docs/downloads/05/tbl_water_marovoay_ampijoroa.xlsx
+++ b/docs/downloads/05/tbl_water_marovoay_ampijoroa.xlsx
@@ -405,12 +405,6 @@
           <t>Puits (margelle)</t>
         </is>
       </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>2.8</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -495,12 +489,6 @@
           <t>Eau courante dans la maison/dans la cour</t>
         </is>
       </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-      <c r="D8">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -512,12 +500,6 @@
         <is>
           <t>Impluvium</t>
         </is>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>0.2</v>
       </c>
     </row>
     <row r="10">
